--- a/feedback_surveys/031_child_play_date_feedback--feedback_surveys.xlsx
+++ b/feedback_surveys/031_child_play_date_feedback--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -839,8 +839,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -868,12 +868,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'excellent_-_everyone_had_fun',_'value':_'excellent'}</t>
+          <t>excellent_-_everyone_had_fun</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent - Everyone had fun', 'value': 'excellent'}</t>
+          <t>Excellent - Everyone had fun</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'good_-_mostly_positive',_'value':_'good'}</t>
+          <t>good_-_mostly_positive</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Good - Mostly positive', 'value': 'good'}</t>
+          <t>Good - Mostly positive</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'fair_-_some_issues',_'value':_'fair'}</t>
+          <t>fair_-_some_issues</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Fair - Some issues', 'value': 'fair'}</t>
+          <t>Fair - Some issues</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'poor_-_not_recommended',_'value':_'poor'}</t>
+          <t>poor_-_not_recommended</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Poor - Not recommended', 'value': 'poor'}</t>
+          <t>Poor - Not recommended</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'art_and_creative_crafts',_'value':_'art'}</t>
+          <t>art_and_creative_crafts</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Art and Creative Crafts', 'value': 'art'}</t>
+          <t>Art and Creative Crafts</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'reading_and_storytelling',_'value':_'reading'}</t>
+          <t>reading_and_storytelling</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Reading and Storytelling', 'value': 'reading'}</t>
+          <t>Reading and Storytelling</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'outdoor_and_physical_play',_'value':_'outdoor'}</t>
+          <t>outdoor_and_physical_play</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Outdoor and Physical Play', 'value': 'outdoor'}</t>
+          <t>Outdoor and Physical Play</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'board_games_and_puzzles',_'value':_'games'}</t>
+          <t>board_games_and_puzzles</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Board Games and Puzzles', 'value': 'games'}</t>
+          <t>Board Games and Puzzles</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'building_blocks_and_construction',_'value':_'blocks'}</t>
+          <t>building_blocks_and_construction</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Building Blocks and Construction', 'value': 'blocks'}</t>
+          <t>Building Blocks and Construction</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_definitely',_'value':_true}</t>
+          <t>yes_-_definitely</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - Definitely', 'value': True}</t>
+          <t>Yes - Definitely</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'no_-_not_interested',_'value':_false}</t>
+          <t>no_-_not_interested</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'No - Not interested', 'value': False}</t>
+          <t>No - Not interested</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'unsure_-_need_to_ask_child',_'value':_'unsure'}</t>
+          <t>unsure_-_need_to_ask_child</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Unsure - Need to ask child', 'value': 'unsure'}</t>
+          <t>Unsure - Need to ask child</t>
         </is>
       </c>
     </row>
